--- a/data/trans_dic/IP11-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP11-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han sufrido algún accidente por el cual necesitase asiscencia sanitaria en los últimos 12 meses.</t>
+          <t>Menores que han sufrido algún accidente por el cual necesitase asiscencia sanitaria en los últimos 12 meses. (tasa de respuesta: 99,87%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,73; 13,59</t>
+          <t>5,85; 13,66</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,55; 10,43</t>
+          <t>3,56; 10,58</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,56; 9,55</t>
+          <t>2,57; 9,18</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,15; 7,12</t>
+          <t>1,04; 6,25</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,43; 13,08</t>
+          <t>5,34; 12,73</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,61; 15,51</t>
+          <t>6,86; 15,64</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,89; 11,07</t>
+          <t>3,71; 11,04</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,42; 4,19</t>
+          <t>0,39; 4,24</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,47; 12,04</t>
+          <t>6,55; 12,0</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6,15; 11,76</t>
+          <t>6,21; 11,45</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,93; 8,78</t>
+          <t>3,71; 8,72</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,04; 4,22</t>
+          <t>1,2; 4,35</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,87; 5,85</t>
+          <t>2,05; 5,95</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,33; 14,11</t>
+          <t>7,13; 14,27</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,4; 6,87</t>
+          <t>2,43; 7,09</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,87; 4,78</t>
+          <t>1,07; 4,9</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,07; 9,52</t>
+          <t>3,98; 9,54</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,07; 12,08</t>
+          <t>6,07; 12,39</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,03; 7,8</t>
+          <t>2,72; 7,74</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,02; 4,89</t>
+          <t>0,96; 5,06</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,54; 6,97</t>
+          <t>3,67; 7,25</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,35; 11,99</t>
+          <t>7,36; 12,08</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,32; 6,37</t>
+          <t>3,17; 6,34</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,31; 4,0</t>
+          <t>1,27; 4,0</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,31; 8,26</t>
+          <t>2,34; 8,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,02; 9,18</t>
+          <t>2,87; 8,93</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,33; 5,34</t>
+          <t>1,28; 5,4</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,6; 6,62</t>
+          <t>1,57; 6,55</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,23; 9,45</t>
+          <t>3,54; 9,82</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,55; 15,54</t>
+          <t>7,41; 14,9</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,63; 7,78</t>
+          <t>2,43; 7,69</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,01; 8,03</t>
+          <t>1,88; 8,18</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,41; 7,71</t>
+          <t>3,56; 7,93</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,18; 10,79</t>
+          <t>6,07; 11,05</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,47; 5,73</t>
+          <t>2,44; 5,81</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,31; 6,06</t>
+          <t>2,27; 6,12</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,25; 7,16</t>
+          <t>2,21; 7,2</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,55; 9,23</t>
+          <t>3,6; 9,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,49</t>
+          <t>0,36; 3,92</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,4; 3,97</t>
+          <t>0,45; 3,81</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,16; 8,1</t>
+          <t>3,14; 8,15</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,36; 13,24</t>
+          <t>6,5; 13,31</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,34; 8,99</t>
+          <t>3,51; 9,11</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,1; 7,5</t>
+          <t>2,17; 7,63</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,27; 6,59</t>
+          <t>3,19; 6,56</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5,71; 10,04</t>
+          <t>5,6; 9,95</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,22; 5,53</t>
+          <t>2,32; 5,41</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,56; 4,68</t>
+          <t>1,64; 4,92</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,85; 6,65</t>
+          <t>3,99; 6,73</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,81; 8,93</t>
+          <t>5,82; 8,88</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,3; 4,48</t>
+          <t>2,42; 4,61</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,74; 3,81</t>
+          <t>1,61; 3,63</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,08; 8,09</t>
+          <t>5,1; 8,01</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,14; 11,67</t>
+          <t>8,08; 11,74</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,12; 7,04</t>
+          <t>4,21; 7,05</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,14; 4,62</t>
+          <t>2,17; 4,55</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,98; 6,9</t>
+          <t>4,91; 6,94</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7,41; 9,83</t>
+          <t>7,37; 9,83</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,64; 5,45</t>
+          <t>3,62; 5,35</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,16; 3,83</t>
+          <t>2,14; 3,74</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que han sufrido algún accidente por el cual necesitase asiscencia sanitaria en los últimos 12 meses. (tasa de respuesta: 99,87%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>12888</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>9073</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>6996</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>3497</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>13243</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>16370</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>9981</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>2308</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>26130</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>25443</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>16976</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>5805</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>8119; 18951</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>4960; 14738</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>3438; 12275</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1221; 7326</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>8173; 19487</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>10610; 24190</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>5467; 16278</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>547; 5953</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>19109; 35006</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>18262; 33665</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>10420; 24512</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>3103; 11219</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>7045</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>21431</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>8955</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>4532</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>13703</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>19495</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>11082</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>5899</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>20748</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>40926</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>20037</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>10431</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>4007; 11613</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>14713; 29454</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>5028; 14645</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>2046; 9342</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>8454; 20236</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>13577; 27737</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>6076; 17320</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>2428; 12844</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>14939; 29542</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>31684; 51951</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>13646; 27288</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>5659; 17785</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>6332</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>8499</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>4465</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>6546</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>8895</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>18141</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>7892</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>8289</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>15227</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>26639</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>12356</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>14835</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>3220; 11257</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>4440; 13833</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1992; 8421</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>2982; 12441</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>5292; 14699</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>12303; 24732</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>4053; 12821</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>3483; 15165</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>10242; 22797</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>19496; 35455</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>7888; 18741</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>8517; 22960</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>9039</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>12709</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2954</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>2577</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>10685</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>19371</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>11769</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>7538</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>19724</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>32080</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>14723</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>10115</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>4634; 15075</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>7575; 19194</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>747; 8061</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>761; 6398</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>6535; 16928</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>13433; 27498</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>7211; 18739</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>3928; 13835</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>13287; 27372</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>23324; 41490</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>9538; 22281</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>5731; 17164</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>35304</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>51712</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>23369</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>17151</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>46525</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>73377</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>40724</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>24034</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>81829</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>125089</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>64093</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>41185</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>27177; 45823</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>41383; 63152</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>16956; 32398</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>10722; 24148</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>36857; 57878</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>60681; 88164</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>31315; 52415</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>16495; 34648</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>68914; 97386</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>107822; 143696</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>52335; 77356</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>30595; 53334</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP11-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP11-Habitat-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,85; 13,66</t>
+          <t>5,7; 13,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,56; 10,58</t>
+          <t>3,49; 10,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,57; 9,18</t>
+          <t>2,48; 8,89</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,04; 6,25</t>
+          <t>1,15; 6,37</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,34; 12,73</t>
+          <t>5,31; 13,01</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,86; 15,64</t>
+          <t>6,96; 15,54</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,71; 11,04</t>
+          <t>3,59; 10,98</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,39; 4,24</t>
+          <t>0,42; 4,14</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,55; 12,0</t>
+          <t>6,45; 11,83</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6,21; 11,45</t>
+          <t>6,2; 11,33</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,71; 8,72</t>
+          <t>3,82; 8,48</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,2; 4,35</t>
+          <t>1,06; 4,12</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,05; 5,95</t>
+          <t>1,97; 6,26</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,13; 14,27</t>
+          <t>7,28; 14,32</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,43; 7,09</t>
+          <t>2,41; 6,64</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,07; 4,9</t>
+          <t>0,84; 5,09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,98; 9,54</t>
+          <t>3,97; 9,26</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,07; 12,39</t>
+          <t>5,84; 12,29</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,72; 7,74</t>
+          <t>2,89; 7,41</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,96; 5,06</t>
+          <t>0,95; 4,7</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,67; 7,25</t>
+          <t>3,55; 6,81</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,36; 12,08</t>
+          <t>7,38; 11,92</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,17; 6,34</t>
+          <t>3,25; 6,47</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,27; 4,0</t>
+          <t>1,21; 3,99</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,96%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,34; 8,17</t>
+          <t>2,06; 7,95</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,87; 8,93</t>
+          <t>3,13; 9,09</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,28; 5,4</t>
+          <t>1,29; 5,58</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,57; 6,55</t>
+          <t>1,35; 6,45</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,54; 9,82</t>
+          <t>3,22; 9,56</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,41; 14,9</t>
+          <t>7,56; 15,6</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,43; 7,69</t>
+          <t>2,68; 7,86</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,88; 8,18</t>
+          <t>2,13; 8,52</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,56; 7,93</t>
+          <t>3,54; 7,82</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,07; 11,05</t>
+          <t>6,15; 11,25</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,44; 5,81</t>
+          <t>2,52; 5,99</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,27; 6,12</t>
+          <t>2,41; 6,59</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,21; 7,2</t>
+          <t>2,43; 6,89</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,6; 9,13</t>
+          <t>3,75; 9,3</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,92</t>
+          <t>0,36; 3,63</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,45; 3,81</t>
+          <t>0,4; 3,74</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,14; 8,15</t>
+          <t>3,14; 8,02</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,5; 13,31</t>
+          <t>5,91; 13,21</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,51; 9,11</t>
+          <t>3,46; 9,12</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,17; 7,63</t>
+          <t>1,93; 7,32</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,19; 6,56</t>
+          <t>3,32; 6,55</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5,6; 9,95</t>
+          <t>5,68; 10,14</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,32; 5,41</t>
+          <t>2,28; 5,68</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,64; 4,92</t>
+          <t>1,67; 4,77</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,99; 6,73</t>
+          <t>3,85; 6,71</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,82; 8,88</t>
+          <t>5,71; 9,15</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,42; 4,61</t>
+          <t>2,45; 4,53</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,61; 3,63</t>
+          <t>1,6; 3,78</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,1; 8,01</t>
+          <t>5,07; 8,14</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,08; 11,74</t>
+          <t>8,06; 11,66</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,21; 7,05</t>
+          <t>4,22; 7,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,17; 4,55</t>
+          <t>2,15; 4,61</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,91; 6,94</t>
+          <t>4,92; 6,85</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7,37; 9,83</t>
+          <t>7,43; 9,73</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,62; 5,35</t>
+          <t>3,65; 5,32</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,14; 3,74</t>
+          <t>2,1; 3,69</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>8119; 18951</t>
+          <t>7912; 19143</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4960; 14738</t>
+          <t>4865; 14710</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3438; 12275</t>
+          <t>3320; 11889</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1221; 7326</t>
+          <t>1348; 7465</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>8173; 19487</t>
+          <t>8127; 19910</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10610; 24190</t>
+          <t>10761; 24030</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5467; 16278</t>
+          <t>5296; 16188</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>547; 5953</t>
+          <t>593; 5807</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>19109; 35006</t>
+          <t>18814; 34523</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>18262; 33665</t>
+          <t>18231; 33311</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10420; 24512</t>
+          <t>10740; 23840</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3103; 11219</t>
+          <t>2720; 10612</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4007; 11613</t>
+          <t>3837; 12224</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14713; 29454</t>
+          <t>15017; 29556</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5028; 14645</t>
+          <t>4982; 13729</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2046; 9342</t>
+          <t>1602; 9702</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8454; 20236</t>
+          <t>8414; 19649</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13577; 27737</t>
+          <t>13082; 27515</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6076; 17320</t>
+          <t>6459; 16580</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2428; 12844</t>
+          <t>2424; 11939</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14939; 29542</t>
+          <t>14459; 27734</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>31684; 51951</t>
+          <t>31762; 51272</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13646; 27288</t>
+          <t>13993; 27825</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5659; 17785</t>
+          <t>5366; 17721</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3220; 11257</t>
+          <t>2842; 10961</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4440; 13833</t>
+          <t>4851; 14092</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1992; 8421</t>
+          <t>2014; 8711</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2982; 12441</t>
+          <t>2559; 12198</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5292; 14699</t>
+          <t>4818; 14314</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12303; 24732</t>
+          <t>12543; 25888</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4053; 12821</t>
+          <t>4474; 13097</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3483; 15165</t>
+          <t>3947; 15781</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>10242; 22797</t>
+          <t>10170; 22481</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>19496; 35455</t>
+          <t>19735; 36110</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7888; 18741</t>
+          <t>8120; 19331</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>8517; 22960</t>
+          <t>9039; 24661</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4634; 15075</t>
+          <t>5085; 14413</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7575; 19194</t>
+          <t>7881; 19553</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>747; 8061</t>
+          <t>738; 7461</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>761; 6398</t>
+          <t>670; 6274</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6535; 16928</t>
+          <t>6522; 16664</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>13433; 27498</t>
+          <t>12218; 27291</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7211; 18739</t>
+          <t>7116; 18769</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3928; 13835</t>
+          <t>3496; 13259</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>13287; 27372</t>
+          <t>13862; 27328</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>23324; 41490</t>
+          <t>23680; 42258</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9538; 22281</t>
+          <t>9366; 23363</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>5731; 17164</t>
+          <t>5848; 16652</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>27177; 45823</t>
+          <t>26187; 45694</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>41383; 63152</t>
+          <t>40579; 65077</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>16956; 32398</t>
+          <t>17224; 31776</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10722; 24148</t>
+          <t>10652; 25105</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>36857; 57878</t>
+          <t>36605; 58829</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>60681; 88164</t>
+          <t>60540; 87567</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>31315; 52415</t>
+          <t>31377; 52052</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>16495; 34648</t>
+          <t>16368; 35058</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>68914; 97386</t>
+          <t>69001; 96090</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>107822; 143696</t>
+          <t>108681; 142229</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>52335; 77356</t>
+          <t>52697; 76910</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>30595; 53334</t>
+          <t>29937; 52614</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP11-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP11-Habitat-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,54 +649,54 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>8,65%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>10,58%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>6,77%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1,76%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>9,29%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>6,51%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>5,23%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2,98%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>3,01%</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>8,95%</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>8,65%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>10,58%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>6,77%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1,64%</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>8,95%</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>8,65%</t>
-        </is>
-      </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
           <t>6,04%</t>
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,7; 13,8</t>
+          <t>5,43; 13,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,49; 10,56</t>
+          <t>6,61; 15,51</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,48; 8,89</t>
+          <t>3,89; 11,07</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,15; 6,37</t>
+          <t>0,43; 4,43</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,31; 13,01</t>
+          <t>5,73; 13,59</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,96; 15,54</t>
+          <t>3,55; 10,43</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,59; 10,98</t>
+          <t>2,56; 9,55</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,42; 4,14</t>
+          <t>1,12; 7,57</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,45; 11,83</t>
+          <t>6,47; 12,04</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6,2; 11,33</t>
+          <t>6,15; 11,76</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,82; 8,48</t>
+          <t>3,93; 8,78</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,06; 4,12</t>
+          <t>1,09; 4,51</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>6,46%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>8,71%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>4,95%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>2,45%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>3,61%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>10,39%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>4,33%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>2,38%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>6,46%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>8,71%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>4,95%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,47%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,97; 6,26</t>
+          <t>4,07; 9,52</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,28; 14,32</t>
+          <t>6,07; 12,08</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,41; 6,64</t>
+          <t>3,03; 7,8</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,84; 5,09</t>
+          <t>1,07; 5,17</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,97; 9,26</t>
+          <t>1,87; 5,85</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,84; 12,29</t>
+          <t>7,33; 14,11</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,89; 7,41</t>
+          <t>2,4; 6,87</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,95; 4,7</t>
+          <t>0,97; 5,07</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,55; 6,81</t>
+          <t>3,54; 6,97</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,38; 11,92</t>
+          <t>7,35; 11,99</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,25; 6,47</t>
+          <t>3,32; 6,37</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,21; 3,99</t>
+          <t>1,34; 4,21</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>5,94%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>10,93%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>4,73%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>4,45%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>4,59%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>5,48%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>2,86%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3,46%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>5,94%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>10,93%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>4,73%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,27%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,06; 7,95</t>
+          <t>3,23; 9,45</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,13; 9,09</t>
+          <t>7,55; 15,54</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,29; 5,58</t>
+          <t>2,63; 7,78</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,35; 6,45</t>
+          <t>2,01; 8,09</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,22; 9,56</t>
+          <t>2,31; 8,26</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,56; 15,6</t>
+          <t>3,02; 9,18</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,68; 7,86</t>
+          <t>1,33; 5,34</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,13; 8,52</t>
+          <t>1,87; 7,46</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,54; 7,82</t>
+          <t>3,41; 7,71</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,15; 11,25</t>
+          <t>6,18; 10,79</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,52; 5,99</t>
+          <t>2,47; 5,73</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,41; 6,59</t>
+          <t>2,53; 6,69</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>5,14%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>9,38%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5,72%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3,98%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>4,32%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>6,04%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>1,44%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1,53%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>5,14%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>9,38%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>5,72%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,43; 6,89</t>
+          <t>3,16; 8,1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,75; 9,3</t>
+          <t>6,36; 13,24</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,63</t>
+          <t>3,34; 8,99</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,4; 3,74</t>
+          <t>2,01; 7,18</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,14; 8,02</t>
+          <t>2,25; 7,16</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,91; 13,21</t>
+          <t>3,55; 9,23</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,46; 9,12</t>
+          <t>0,36; 3,49</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,93; 7,32</t>
+          <t>0,38; 3,94</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,32; 6,55</t>
+          <t>3,27; 6,59</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5,68; 10,14</t>
+          <t>5,71; 10,04</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,28; 5,68</t>
+          <t>2,22; 5,53</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,67; 4,77</t>
+          <t>1,47; 4,5</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>6,44%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>9,77%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>5,48%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>3,18%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>5,18%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>7,27%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>3,33%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2,58%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>6,44%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>9,77%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>5,48%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,85; 6,71</t>
+          <t>5,08; 8,09</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,71; 9,15</t>
+          <t>8,14; 11,67</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,45; 4,53</t>
+          <t>4,12; 7,04</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,6; 3,78</t>
+          <t>2,14; 4,67</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,07; 8,14</t>
+          <t>3,85; 6,65</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,06; 11,66</t>
+          <t>5,81; 8,93</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,22; 7,0</t>
+          <t>2,3; 4,48</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,15; 4,61</t>
+          <t>1,89; 4,08</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,92; 6,85</t>
+          <t>4,98; 6,9</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7,43; 9,73</t>
+          <t>7,41; 9,83</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,65; 5,32</t>
+          <t>3,64; 5,45</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,1; 3,69</t>
+          <t>2,24; 3,81</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1514,37 +1514,37 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>13243</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>16370</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>9981</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>2213</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>12888</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>9073</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>6996</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>3497</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>13243</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>16370</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>9981</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>3644</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5805</t>
+          <t>5857</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7912; 19143</t>
+          <t>8313; 20021</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4865; 14710</t>
+          <t>10217; 23992</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3320; 11889</t>
+          <t>5727; 16317</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1348; 7465</t>
+          <t>538; 5572</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>8127; 19910</t>
+          <t>7944; 18852</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10761; 24030</t>
+          <t>4947; 14534</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5296; 16188</t>
+          <t>3417; 12773</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>593; 5807</t>
+          <t>1355; 9165</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>18814; 34523</t>
+          <t>18879; 35122</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>18231; 33311</t>
+          <t>18093; 34592</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10740; 23840</t>
+          <t>11039; 24686</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2720; 10612</t>
+          <t>2702; 11133</t>
         </is>
       </c>
     </row>
@@ -1717,37 +1717,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>14</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>13703</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>19495</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>11082</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>5795</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>7045</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>21431</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>8955</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>4532</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>13703</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>19495</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>11082</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>5899</t>
+          <t>4615</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>10431</t>
+          <t>10410</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3837; 12224</t>
+          <t>8633; 20194</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15017; 29556</t>
+          <t>13582; 27032</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4982; 13729</t>
+          <t>6789; 17443</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1602; 9702</t>
+          <t>2529; 12216</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8414; 19649</t>
+          <t>3646; 11417</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13082; 27515</t>
+          <t>15136; 29125</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6459; 16580</t>
+          <t>4964; 14198</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2424; 11939</t>
+          <t>1782; 9341</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14459; 27734</t>
+          <t>14422; 28390</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>31762; 51272</t>
+          <t>31635; 51577</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13993; 27825</t>
+          <t>14283; 27414</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5366; 17721</t>
+          <t>5656; 17710</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>10</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>8895</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>18141</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>7892</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>7498</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>6332</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>8499</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>4465</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>6546</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>8895</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>18141</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>7892</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8289</t>
+          <t>6352</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>14835</t>
+          <t>13850</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2842; 10961</t>
+          <t>4839; 14147</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4851; 14092</t>
+          <t>12525; 25801</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2014; 8711</t>
+          <t>4383; 12971</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2559; 12198</t>
+          <t>3380; 13619</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4818; 14314</t>
+          <t>3181; 11378</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12543; 25888</t>
+          <t>4679; 14225</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4474; 13097</t>
+          <t>2078; 8324</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3947; 15781</t>
+          <t>2914; 11631</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>10170; 22481</t>
+          <t>9795; 22163</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>19735; 36110</t>
+          <t>19823; 34642</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8120; 19331</t>
+          <t>7962; 18480</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>9039; 24661</t>
+          <t>8189; 21691</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>10685</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>19371</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>11769</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>6746</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>9039</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>12709</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>2954</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2577</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>10685</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>19371</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>11769</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>7538</t>
+          <t>2572</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>10115</t>
+          <t>9318</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5085; 14413</t>
+          <t>6566; 16831</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7881; 19553</t>
+          <t>13136; 27344</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>738; 7461</t>
+          <t>6877; 18505</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>670; 6274</t>
+          <t>3399; 12153</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6522; 16664</t>
+          <t>4704; 14983</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>12218; 27291</t>
+          <t>7475; 19410</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7116; 18769</t>
+          <t>739; 7188</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3496; 13259</t>
+          <t>637; 6588</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>13862; 27328</t>
+          <t>13631; 27507</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>23680; 42258</t>
+          <t>23817; 41870</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9366; 23363</t>
+          <t>9118; 22745</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>5848; 16652</t>
+          <t>4953; 15159</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>26</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>46525</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>73377</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>40724</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>22251</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>35304</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>51712</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>23369</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>17151</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>46525</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>73377</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>40724</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>24034</t>
+          <t>17184</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>41185</t>
+          <t>39435</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>26187; 45694</t>
+          <t>36682; 58494</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>40579; 65077</t>
+          <t>61136; 87643</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>17224; 31776</t>
+          <t>30622; 52365</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10652; 25105</t>
+          <t>14992; 32709</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>36605; 58829</t>
+          <t>26221; 45310</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>60540; 87567</t>
+          <t>41292; 63464</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>31377; 52052</t>
+          <t>16176; 31456</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>16368; 35058</t>
+          <t>11864; 25644</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>69001; 96090</t>
+          <t>69862; 96898</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>108681; 142229</t>
+          <t>108382; 143766</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>52697; 76910</t>
+          <t>52656; 78791</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>29937; 52614</t>
+          <t>29723; 50648</t>
         </is>
       </c>
     </row>
